--- a/data/trans_orig/P36BPD08_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de vasos de vino que consumen a la semana en 2023</t>
+          <t>Población según el número de vasos de vino que consumen a la semana en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>273984</t>
+          <t>274555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>292128</t>
+          <t>293049</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279898</t>
+          <t>279583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286263</t>
+          <t>286249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558070</t>
+          <t>558343</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>576696</t>
+          <t>578009</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19642</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8554</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23581</t>
+          <t>22486</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25997</t>
+          <t>25339</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>433655</t>
+          <t>430340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>475918</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488613</t>
+          <t>489326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502602</t>
+          <t>502310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927637</t>
+          <t>929300</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>974733</t>
+          <t>972894</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,33%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74562</t>
+          <t>76295</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92158</t>
+          <t>91021</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16756</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>509</t>
+          <t>522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>18537</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263948</t>
+          <t>265360</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285560</t>
+          <t>285396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>338105</t>
+          <t>338034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>346435</t>
+          <t>346369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>605486</t>
+          <t>606246</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>628545</t>
+          <t>628918</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11183</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>25846</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>681</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>6855</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12786</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30153</t>
+          <t>29371</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15971</t>
+          <t>15287</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31482</t>
+          <t>30488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>33796</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>268775</t>
+          <t>270195</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>289970</t>
+          <t>290588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>461092</t>
+          <t>461275</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>472474</t>
+          <t>472224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>736404</t>
+          <t>734714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>761457</t>
+          <t>760654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>7932</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23906</t>
+          <t>23025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9882</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>11552</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22780</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26078</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146615</t>
+          <t>146498</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161621</t>
+          <t>161467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>192932</t>
+          <t>193021</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201451</t>
+          <t>201453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343533</t>
+          <t>343250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>360316</t>
+          <t>360183</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>8663</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9284</t>
+          <t>9307</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14537</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>29406</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>236567</t>
+          <t>235910</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>252112</t>
+          <t>251620</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>248340</t>
+          <t>247720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>254894</t>
+          <t>254931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>488264</t>
+          <t>488129</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>504571</t>
+          <t>504408</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,77%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>6160</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16816</t>
+          <t>16493</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>535</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7651</t>
+          <t>8140</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>19406</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>9405</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>21547</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11435</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24114</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>568025</t>
+          <t>568498</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>592192</t>
+          <t>592826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>819842</t>
+          <t>820268</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>840587</t>
+          <t>840241</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1392950</t>
+          <t>1393259</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1433657</t>
+          <t>1434508</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15906</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22289</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49155</t>
+          <t>48719</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10742</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>14879</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>14424</t>
+          <t>14694</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>35942</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>681379</t>
+          <t>679298</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>848837</t>
+          <t>844426</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>657087</t>
+          <t>659815</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>681025</t>
+          <t>682266</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1376539</t>
+          <t>1376715</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1513725</t>
+          <t>1517888</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8603</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>38790</t>
+          <t>40081</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11593</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25123</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>56090</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>66262</t>
+          <t>75325</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>214779</t>
+          <t>214474</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20397</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39259</t>
+          <t>37359</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>108282</t>
+          <t>102672</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>217878</t>
+          <t>219183</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2977203</t>
+          <t>2980225</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3127482</t>
+          <t>3136197</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3522376</t>
+          <t>3522576</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3567345</t>
+          <t>3567237</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4443,17 +4443,17 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>6577630</t>
+          <t>6577631</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6520156</t>
+          <t>6521436</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6651074</t>
+          <t>6649045</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>118028</t>
+          <t>123873</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>194280</t>
+          <t>196118</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>49209</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>75865</t>
+          <t>76199</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>184075</t>
+          <t>185455</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>256138</t>
+          <t>259999</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>199087</t>
+          <t>196775</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>293360</t>
+          <t>292243</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>41912</t>
+          <t>42223</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>69937</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>266346</t>
+          <t>267560</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>348439</t>
+          <t>350513</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7111232</t>
+          <t>7111233</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">

--- a/data/trans_orig/P36BPD08_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>284884</t>
+          <t>291845</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>274555</t>
+          <t>282264</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>293049</t>
+          <t>299729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>283684</t>
+          <t>307982</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>279583</t>
+          <t>302001</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>286249</t>
+          <t>311126</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>568567</t>
+          <t>599827</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>558343</t>
+          <t>588469</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>578009</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11719</t>
+          <t>11210</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21835</t>
+          <t>24067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14840</t>
+          <t>15790</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>10081</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17941</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>12782</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25339</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>289137</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>289137</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289137</t>
+          <t>315581</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>600579</t>
+          <t>634426</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>600579</t>
+          <t>634426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>600579</t>
+          <t>634426</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>457359</t>
+          <t>470549</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>430340</t>
+          <t>447008</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>475918</t>
+          <t>487243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>496638</t>
+          <t>527424</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>489326</t>
+          <t>519455</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>502310</t>
+          <t>533038</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>953996</t>
+          <t>997973</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>929300</t>
+          <t>972460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>972894</t>
+          <t>1015568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>50517</t>
+          <t>49038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>33611</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76295</t>
+          <t>72769</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>16355</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>66175</t>
+          <t>65393</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>48904</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91021</t>
+          <t>89781</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15831</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2036</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5428</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6199</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>517070</t>
+          <t>529315</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517070</t>
+          <t>529315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517070</t>
+          <t>529315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>514311</t>
+          <t>545816</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>514311</t>
+          <t>545816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>514311</t>
+          <t>545816</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1031381</t>
+          <t>1075131</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1031381</t>
+          <t>1075131</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1031381</t>
+          <t>1075131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,27 +1637,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>275724</t>
+          <t>276768</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265360</t>
+          <t>265900</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285396</t>
+          <t>285388</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>343275</t>
+          <t>350603</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>338034</t>
+          <t>344221</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>346369</t>
+          <t>353597</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>618999</t>
+          <t>627371</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>606246</t>
+          <t>616595</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>628918</t>
+          <t>637687</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17431</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11084</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25846</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>670</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20247</t>
+          <t>19583</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>12921</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29371</t>
+          <t>29293</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21689</t>
+          <t>21245</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30488</t>
+          <t>30872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24724</t>
+          <t>24243</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>17278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>33796</t>
+          <t>33522</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,99%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>314843</t>
+          <t>314816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>314843</t>
+          <t>314816</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>314843</t>
+          <t>314816</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>663971</t>
+          <t>671197</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>663971</t>
+          <t>671197</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>663971</t>
+          <t>671197</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>281226</t>
+          <t>337691</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>270195</t>
+          <t>325827</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>290588</t>
+          <t>347265</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>468458</t>
+          <t>413519</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>461275</t>
+          <t>406706</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>472224</t>
+          <t>417463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>749684</t>
+          <t>751211</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>734714</t>
+          <t>737579</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>760654</t>
+          <t>761784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14405</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7932</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23025</t>
+          <t>24880</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>21165</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11552</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29834</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9364</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>16966</t>
+          <t>20368</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>13146</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>30623</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>310414</t>
+          <t>370782</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>310414</t>
+          <t>370782</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>310414</t>
+          <t>370782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>786132</t>
+          <t>792744</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>786132</t>
+          <t>792744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>786132</t>
+          <t>792744</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>154964</t>
+          <t>179489</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>146498</t>
+          <t>168627</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161467</t>
+          <t>186030</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>197829</t>
+          <t>215812</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193021</t>
+          <t>210484</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>201453</t>
+          <t>219606</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>352793</t>
+          <t>395302</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>343250</t>
+          <t>384321</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>360183</t>
+          <t>404285</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7732</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2649</t>
+          <t>2690</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12658</t>
+          <t>13561</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>8994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>19955</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>15371</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23530</t>
+          <t>26321</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9307</t>
+          <t>9769</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>20890</t>
+          <t>22897</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14704</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29406</t>
+          <t>32625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,56%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>204936</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>204936</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>178067</t>
+          <t>204936</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>386341</t>
+          <t>431760</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>386341</t>
+          <t>431760</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>386341</t>
+          <t>431760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>245191</t>
+          <t>246475</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235910</t>
+          <t>238359</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>251620</t>
+          <t>252977</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>252220</t>
+          <t>258931</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>247720</t>
+          <t>254782</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>254931</t>
+          <t>261377</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>497412</t>
+          <t>505406</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>488129</t>
+          <t>495718</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>504408</t>
+          <t>512169</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -3118,32 +3118,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6143</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16493</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2042</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>535</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,32 +3188,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19406</t>
+          <t>19619</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -3231,32 +3231,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>13985</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21547</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2787</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>957</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,22 +3301,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11435</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24040</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>581716</t>
+          <t>667646</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>568498</t>
+          <t>651924</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>592826</t>
+          <t>679561</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>829938</t>
+          <t>744390</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>820268</t>
+          <t>733793</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>840241</t>
+          <t>751956</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1411654</t>
+          <t>1412035</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1393259</t>
+          <t>1391482</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1434508</t>
+          <t>1427233</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>95,95%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>29174</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15906</t>
+          <t>19663</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35646</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>13051</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>34855</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>31505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>48719</t>
+          <t>58431</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -3687,102 +3687,102 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>16500</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>25008</t>
+          <t>28744</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,01%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>13550</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>8097</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>22896</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>33282</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>23815</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>45608</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>8220</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>3303</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>14879</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>24720</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>14694</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>35143</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>622127</t>
+          <t>716551</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>622127</t>
+          <t>716551</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>622127</t>
+          <t>716551</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>849102</t>
+          <t>770991</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>849102</t>
+          <t>770991</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>849102</t>
+          <t>770991</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1471229</t>
+          <t>1487542</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1471229</t>
+          <t>1487542</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1471229</t>
+          <t>1487542</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3917,32 +3917,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>753115</t>
+          <t>601621</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>679298</t>
+          <t>571705</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>844426</t>
+          <t>624005</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,32 +3952,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>671410</t>
+          <t>780075</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>659815</t>
+          <t>767772</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>682266</t>
+          <t>792407</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,32 +3987,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1424525</t>
+          <t>1381697</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1376715</t>
+          <t>1351299</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1517888</t>
+          <t>1411575</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>86,72%</t>
         </is>
       </c>
     </row>
@@ -4030,32 +4030,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>24309</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>10014</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>40081</t>
+          <t>41711</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4065,32 +4065,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11593</t>
+          <t>12690</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25202</t>
+          <t>28578</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4100,32 +4100,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>41950</t>
+          <t>46459</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>34234</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>56090</t>
+          <t>60585</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4143,32 +4143,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>150293</t>
+          <t>168446</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>75325</t>
+          <t>147429</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>214474</t>
+          <t>196545</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4178,32 +4178,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>28140</t>
+          <t>31057</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20397</t>
+          <t>22066</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>41559</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4213,32 +4213,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>178433</t>
+          <t>199503</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>102672</t>
+          <t>170468</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>219183</t>
+          <t>226323</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4256,17 +4256,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>796930</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4291,17 +4291,17 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>717191</t>
+          <t>830728</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>717191</t>
+          <t>830728</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>717191</t>
+          <t>830728</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1644908</t>
+          <t>1627659</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1644908</t>
+          <t>1627659</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1644908</t>
+          <t>1627659</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4373,32 +4373,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>3034178</t>
+          <t>3072085</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2980225</t>
+          <t>3027867</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3136197</t>
+          <t>3108403</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,32 +4408,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3543453</t>
+          <t>3598737</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3522576</t>
+          <t>3577598</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3567237</t>
+          <t>3616682</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4443,32 +4443,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>6577631</t>
+          <t>6670822</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6521436</t>
+          <t>6618733</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6649045</t>
+          <t>6716431</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -4486,32 +4486,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>160392</t>
+          <t>166761</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>123873</t>
+          <t>139503</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>196118</t>
+          <t>197903</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>61456</t>
+          <t>69357</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>49209</t>
+          <t>56763</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>76199</t>
+          <t>83019</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>221848</t>
+          <t>236118</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>185455</t>
+          <t>207006</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>259999</t>
+          <t>271017</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -4599,32 +4599,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>256747</t>
+          <t>284037</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>196775</t>
+          <t>255306</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>292243</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,32 +4634,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>55007</t>
+          <t>63938</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>42223</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4669,32 +4669,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>311754</t>
+          <t>347975</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>267560</t>
+          <t>314030</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>385890</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -4712,17 +4712,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3451317</t>
+          <t>3522883</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3659916</t>
+          <t>3732032</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>7111233</t>
+          <t>7254915</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
